--- a/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023</t>
+          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>47120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49752</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34392</t>
+          <t>35188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54954</t>
+          <t>53345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81401</t>
+          <t>80433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>158006</t>
+          <t>157995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>188863</t>
+          <t>189152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129150</t>
+          <t>127997</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152273</t>
+          <t>151780</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>294690</t>
+          <t>293345</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>334075</t>
+          <t>333843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11191</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56031</t>
+          <t>55776</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>19467</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>43008</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>70329</t>
+          <t>70526</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162496</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>192658</t>
+          <t>192357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135494</t>
+          <t>135320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>153727</t>
+          <t>153747</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>303697</t>
+          <t>305069</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>339523</t>
+          <t>341847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>857</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>962</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8526</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>26740</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,82 +4821,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>7941</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>13910</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>34168</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>25404</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>44471</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>7941</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>4259</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>12849</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>15,76%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>34168</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>25349</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>44513</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>163094</t>
+          <t>161810</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>187254</t>
+          <t>187484</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>59412</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>71208</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>226740</t>
+          <t>227810</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>254932</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>434</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>23720</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>37069</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>60562</t>
+          <t>64930</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>46805</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>92760</t>
+          <t>96259</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>34530</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>58789</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>70281</t>
+          <t>68925</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>112198</t>
+          <t>112364</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>385599</t>
+          <t>382183</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>433696</t>
+          <t>431230</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>433094</t>
+          <t>433453</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>554599</t>
+          <t>550875</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>842660</t>
+          <t>842106</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1005995</t>
+          <t>1007388</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>127374</t>
+          <t>128483</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>129405</t>
+          <t>149920</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>12552</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>41122</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>173021</t>
+          <t>173672</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>198250</t>
+          <t>198171</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>211422</t>
+          <t>212150</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>324968</t>
+          <t>324999</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>402540</t>
+          <t>391916</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>513093</t>
+          <t>514274</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8095,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>15627</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8145,47 +8145,47 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>13286</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>972</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>391</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>392</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -8886,12 +8886,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>29079</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9034,12 +9034,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9112,12 +9112,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>30861</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>20104</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>43021</t>
+          <t>46533</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -9225,12 +9225,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>40459</t>
+          <t>39678</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>66824</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>48708</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>80107</t>
+          <t>81235</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>51572</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>86120</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>307277</t>
+          <t>306463</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>341931</t>
+          <t>341509</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>369295</t>
+          <t>366408</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>419193</t>
+          <t>416788</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>40528</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>23169</t>
+          <t>23766</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>54832</t>
+          <t>55260</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,74 +10035,74 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>9371</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>8243</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>1433</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="S86" s="2" t="inlineStr">
-        <is>
-          <t>1487</t>
-        </is>
-      </c>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
-          <t>9769</t>
-        </is>
-      </c>
-      <c r="U86" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
           <t>0,04%</t>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -10133,12 +10133,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>28395</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>47213</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>18844</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10359,12 +10359,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>64224</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>36976</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>199936</t>
+          <t>198123</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>76473</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>232278</t>
+          <t>259030</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -10472,12 +10472,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>47749</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>27938</t>
+          <t>27879</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>39050</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>69941</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>75561</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>131754</t>
+          <t>131215</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>53285</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>97013</t>
+          <t>99369</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>141761</t>
+          <t>143899</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>215065</t>
+          <t>216351</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -10698,12 +10698,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>162611</t>
+          <t>160141</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>210185</t>
+          <t>210194</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>122044</t>
+          <t>122276</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>203988</t>
+          <t>203231</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>298560</t>
+          <t>292334</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>399060</t>
+          <t>397031</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10811,12 +10811,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1155282</t>
+          <t>1153854</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1232459</t>
+          <t>1232206</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10846,12 +10846,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1384781</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1596533</t>
+          <t>1580876</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>2569872</t>
+          <t>2576781</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2804330</t>
+          <t>2806557</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
@@ -725,22 +725,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8146</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19886</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>19541</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>30869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47120</t>
+          <t>54038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>42694</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>32677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50458</t>
+          <t>56422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,27 +1890,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26746</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1925,22 +1925,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>71336</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53345</t>
+          <t>57945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80433</t>
+          <t>86439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173981</t>
+          <t>183869</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157995</t>
+          <t>163894</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189152</t>
+          <t>198406</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2003,32 +2003,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>140768</t>
+          <t>153244</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127997</t>
+          <t>140776</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151780</t>
+          <t>166260</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,32 +2038,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>314749</t>
+          <t>337113</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>293345</t>
+          <t>315196</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>333843</t>
+          <t>356313</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2081,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264783</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214433</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479216</t>
+          <t>520590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1620</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12630</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>17212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2886,12 +2886,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>33557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3328,32 +3328,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55776</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3363,32 +3363,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20027</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>55705</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>46163</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>70526</t>
+          <t>74155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>185183</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>167965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>192357</t>
+          <t>200213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3476,32 +3476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>145362</t>
+          <t>159226</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135320</t>
+          <t>148010</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>153747</t>
+          <t>167813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,32 +3511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>323325</t>
+          <t>344410</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>305069</t>
+          <t>324862</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>341847</t>
+          <t>363077</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258607</t>
+          <t>272098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>184186</t>
+          <t>202193</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>442793</t>
+          <t>474291</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>797</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>797</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4522,42 +4522,42 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2876</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>19066</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
           <t>5,54%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>7837</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>3160</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>17947</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4688,32 +4688,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,32 +4758,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>37700</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>27491</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>44471</t>
+          <t>47967</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>161810</t>
+          <t>181372</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>187484</t>
+          <t>209455</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>66310</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>59412</t>
+          <t>68741</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>80845</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>242349</t>
+          <t>272854</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227810</t>
+          <t>256207</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>254932</t>
+          <t>286046</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>225849</t>
+          <t>251213</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>81543</t>
+          <t>92847</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5144,32 +5144,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5257,32 +5257,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,32 +5292,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>9577</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6048,32 +6048,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6083,32 +6083,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>21235</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6196,32 +6196,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>46805</t>
+          <t>37907</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>64151</t>
+          <t>63152</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>36067</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>85830</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -6274,32 +6274,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>38063</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>64134</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6309,32 +6309,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>68925</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>86184</t>
+          <t>94741</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>78709</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>112364</t>
+          <t>111883</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -6387,32 +6387,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>411210</t>
+          <t>444248</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>382183</t>
+          <t>420698</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>431230</t>
+          <t>465030</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6422,32 +6422,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>493495</t>
+          <t>318961</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>433453</t>
+          <t>302696</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>550875</t>
+          <t>333654</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>904706</t>
+          <t>763210</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>842106</t>
+          <t>731106</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1007388</t>
+          <t>788270</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>531331</t>
+          <t>568987</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>595995</t>
+          <t>427498</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1127327</t>
+          <t>996485</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6652,32 +6652,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,22 +7365,22 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7408,102 +7408,102 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>5953</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>10604</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>14995</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>8683</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>23972</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>37651</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>3938</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>128483</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>44597</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>10022</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>149920</t>
-        </is>
-      </c>
-      <c r="U63" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -7521,32 +7521,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12330</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7556,32 +7556,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -7634,32 +7634,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7669,32 +7669,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>34804</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7747,32 +7747,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>32569</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>27800</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>41122</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>52009</t>
+          <t>57544</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>45152</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>66038</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -7860,32 +7860,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>186284</t>
+          <t>221682</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>173672</t>
+          <t>206208</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>198171</t>
+          <t>232856</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>294192</t>
+          <t>333264</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>212150</t>
+          <t>316648</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>324999</t>
+          <t>343765</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>480476</t>
+          <t>554946</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>391916</t>
+          <t>534054</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>514274</t>
+          <t>571449</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -7973,17 +7973,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>230111</t>
+          <t>272590</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>386464</t>
+          <t>400794</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>673384</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>774</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>359</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8838,32 +8838,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>342</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -8881,32 +8881,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>28739</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8916,32 +8916,32 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8951,32 +8951,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9029,32 +9029,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9064,32 +9064,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -9107,32 +9107,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>30861</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9142,32 +9142,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9177,32 +9177,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>24624</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>40870</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -9220,32 +9220,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>22246</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9255,32 +9255,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>39678</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>66824</t>
+          <t>70605</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9290,32 +9290,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>63043</t>
+          <t>65656</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>48708</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>83599</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -9333,32 +9333,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>51025</t>
+          <t>56644</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>90080</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9368,32 +9368,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>325345</t>
+          <t>361537</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>306463</t>
+          <t>343670</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>341509</t>
+          <t>377954</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>394998</t>
+          <t>435379</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>366408</t>
+          <t>407912</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>416788</t>
+          <t>457484</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -9446,17 +9446,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>112977</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9481,17 +9481,17 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>413291</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>523929</t>
+          <t>568882</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9563,102 +9563,102 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>6896</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>22667</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>16614</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>5457</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>22466</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>13466</t>
-        </is>
-      </c>
-      <c r="T82" s="2" t="inlineStr">
-        <is>
-          <t>36089</t>
-        </is>
-      </c>
-      <c r="U82" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>41230</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>55260</t>
+          <t>58035</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -10050,32 +10050,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,17 +10085,17 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -10128,27 +10128,27 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -10163,32 +10163,32 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10198,32 +10198,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>35570</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>48681</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -10241,32 +10241,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10276,32 +10276,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>12249</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10311,32 +10311,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -10354,32 +10354,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>63532</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>37466</t>
+          <t>35672</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>198123</t>
+          <t>64180</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10424,32 +10424,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>117846</t>
+          <t>93793</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>76473</t>
+          <t>72879</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>259030</t>
+          <t>120630</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V89" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="W89" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -10467,32 +10467,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>34306</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>24550</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>47749</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10537,32 +10537,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>55977</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>39050</t>
+          <t>43358</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>69941</t>
+          <t>72159</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -10580,22 +10580,22 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>99623</t>
+          <t>103754</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>75870</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>131215</t>
+          <t>133523</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>79176</t>
+          <t>89360</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>75886</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>99369</t>
+          <t>107626</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10650,32 +10650,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>178799</t>
+          <t>193114</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>143899</t>
+          <t>166245</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>216351</t>
+          <t>225018</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -10693,32 +10693,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>184043</t>
+          <t>197898</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>160141</t>
+          <t>172664</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>210194</t>
+          <t>227439</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10728,32 +10728,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>172808</t>
+          <t>187172</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>122276</t>
+          <t>164691</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>203231</t>
+          <t>209242</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10763,32 +10763,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>356851</t>
+          <t>385070</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>292334</t>
+          <t>350004</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>397031</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -10806,32 +10806,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>1195131</t>
+          <t>1306236</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1153854</t>
+          <t>1257855</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1232206</t>
+          <t>1341807</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10841,32 +10841,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>1465472</t>
+          <t>1401676</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>1384781</t>
+          <t>1369324</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1580876</t>
+          <t>1430960</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10876,32 +10876,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2660603</t>
+          <t>2707911</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>2576781</t>
+          <t>2657470</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2806557</t>
+          <t>2759625</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -10919,17 +10919,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>1621320</t>
+          <t>1763147</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1875912</t>
+          <t>1814545</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10989,17 +10989,17 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>3497233</t>
+          <t>3577691</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">

--- a/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
